--- a/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
+++ b/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-13</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -888,7 +888,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-11</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-13</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-02-26</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1677,7 +1677,7 @@
         <is>
           <t>A号屋 (蓝塘道25号)
 4575呎 (4+房)
-(已售)
+(16年-12月)
 $3.02亿
 $65,967/呎</t>
         </is>
@@ -1686,7 +1686,7 @@
         <is>
           <t>A号屋 (蓝塘道27号)
 4575呎 (4+房)
-(已售)
+(18年-06月)
 $3.06亿
 $66,842/呎</t>
         </is>
@@ -1695,7 +1695,7 @@
         <is>
           <t>A号屋 (蓝塘道29号)
 4575呎 (4+房)
-(已售)
+(18年-04月)
 $3.28亿
 $71,694/呎</t>
         </is>
@@ -1713,7 +1713,7 @@
         <is>
           <t>A号屋 (蓝塘道33号)
 4575呎 (4+房)
-(已售)
+(25年-12月)
 $2.28亿
 $49,810/呎</t>
         </is>
@@ -1765,7 +1765,7 @@
         <is>
           <t>B号屋 (蓝塘道25号)
 4602呎 (4+房)
-(已售)
+(19年-05月)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -1774,7 +1774,7 @@
         <is>
           <t>B号屋 (蓝塘道27号)
 4602呎 (4+房)
-(已售)
+(18年-04月)
 $3.38亿
 $73,490/呎</t>
         </is>
@@ -1783,7 +1783,7 @@
         <is>
           <t>B号屋 (蓝塘道29号)
 4602呎 (4+房)
-(已售)
+(24年-06月)
 $2.50亿
 $54,324/呎</t>
         </is>
@@ -1801,7 +1801,7 @@
         <is>
           <t>B号屋 (蓝塘道33号)
 4602呎 (4+房)
-(已售)
+(24年-02月)
 $2.30亿
 $49,978/呎</t>
         </is>
@@ -1810,7 +1810,7 @@
         <is>
           <t>B号屋 (蓝塘道35号)
 4602呎 (4+房)
-(已售)
+(19年-05月)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -1819,7 +1819,7 @@
         <is>
           <t>B号屋 (蓝塘道37号)
 4602呎 (4+房)
-(已售)
+(18年-02月)
 $3.04亿
 $66,015/呎</t>
         </is>
@@ -1828,7 +1828,7 @@
         <is>
           <t>B号屋 (蓝塘道39号)
 4602呎 (3房)
-(已售)
+(21年-07月)
 $3.40亿
 $73,837/呎</t>
         </is>

--- a/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
+++ b/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,22 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -217,13 +233,13 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -601,7 +617,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
+++ b/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
@@ -617,7 +617,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
+++ b/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -620,6 +620,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -677,6 +681,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -727,6 +751,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -777,6 +821,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -823,6 +887,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -869,6 +953,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -915,6 +1019,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -961,6 +1085,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1007,6 +1151,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1053,6 +1217,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1099,6 +1283,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1145,6 +1349,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1191,6 +1415,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1237,6 +1481,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1287,6 +1551,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1333,6 +1617,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1379,6 +1683,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1425,6 +1749,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1471,6 +1815,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1517,13 +1881,33 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1693,7 +2077,7 @@
         <is>
           <t>A号屋 (蓝塘道25号)
 4575呎 (4+房)
-(16年-12月)
+(16年-12月-14日)
 $3.02亿
 $65,967/呎</t>
         </is>
@@ -1702,7 +2086,7 @@
         <is>
           <t>A号屋 (蓝塘道27号)
 4575呎 (4+房)
-(18年-06月)
+(18年-06月-11日)
 $3.06亿
 $66,842/呎</t>
         </is>
@@ -1711,7 +2095,7 @@
         <is>
           <t>A号屋 (蓝塘道29号)
 4575呎 (4+房)
-(18年-04月)
+(18年-04月-18日)
 $3.28亿
 $71,694/呎</t>
         </is>
@@ -1720,7 +2104,7 @@
         <is>
           <t>A号屋 (蓝塘道31号)
 4575呎 (1房)
-(25年-12月)
+(25年-12月-31日)
 $4.47亿
 $97,747/呎</t>
         </is>
@@ -1729,7 +2113,7 @@
         <is>
           <t>A号屋 (蓝塘道33号)
 4575呎 (4+房)
-(25年-12月)
+(25年-12月-21日)
 $2.28亿
 $49,810/呎</t>
         </is>
@@ -1747,7 +2131,7 @@
         <is>
           <t>A号屋 (蓝塘道37号)
 4575呎 (4+房)
-(19年-03月)
+(19年-03月-19日)
 $3.38亿
 $73,923/呎</t>
         </is>
@@ -1756,7 +2140,7 @@
         <is>
           <t>A号屋 (蓝塘道39号)
 4575呎 (4+房)
-(16年-10月)
+(16年-10月-17日)
 $2.88亿
 $63,016/呎</t>
         </is>
@@ -1781,7 +2165,7 @@
         <is>
           <t>B号屋 (蓝塘道25号)
 4602呎 (4+房)
-(19年-05月)
+(19年-05月-13日)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -1790,7 +2174,7 @@
         <is>
           <t>B号屋 (蓝塘道27号)
 4602呎 (4+房)
-(18年-04月)
+(18年-04月-11日)
 $3.38亿
 $73,490/呎</t>
         </is>
@@ -1799,7 +2183,7 @@
         <is>
           <t>B号屋 (蓝塘道29号)
 4602呎 (4+房)
-(24年-06月)
+(24年-06月-04日)
 $2.50亿
 $54,324/呎</t>
         </is>
@@ -1808,7 +2192,7 @@
         <is>
           <t>B号屋 (蓝塘道31号)
 4602呎 (1房)
-(25年-12月)
+(25年-12月-31日)
 $4.47亿
 $97,173/呎</t>
         </is>
@@ -1817,7 +2201,7 @@
         <is>
           <t>B号屋 (蓝塘道33号)
 4602呎 (4+房)
-(24年-02月)
+(24年-02月-08日)
 $2.30亿
 $49,978/呎</t>
         </is>
@@ -1826,7 +2210,7 @@
         <is>
           <t>B号屋 (蓝塘道35号)
 4602呎 (4+房)
-(19年-05月)
+(19年-05月-13日)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -1835,7 +2219,7 @@
         <is>
           <t>B号屋 (蓝塘道37号)
 4602呎 (4+房)
-(18年-02月)
+(18年-02月-26日)
 $3.04亿
 $66,015/呎</t>
         </is>
@@ -1844,7 +2228,7 @@
         <is>
           <t>B号屋 (蓝塘道39号)
 4602呎 (3房)
-(21年-07月)
+(21年-07月-25日)
 $3.40亿
 $73,837/呎</t>
         </is>

--- a/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
+++ b/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
@@ -116,7 +116,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -159,6 +159,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -186,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -240,6 +246,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1442,7 +1451,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>B号屋 (蓝塘道33号)</t>
+          <t>A号屋 (蓝塘道35号)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1457,27 +1466,31 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4602</v>
+        <v>4571</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>230000000</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>49978</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1486,12 +1499,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1501,14 +1514,14 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>A号屋 (蓝塘道35号)</t>
+          <t>B号屋 (蓝塘道35号)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1523,31 +1536,27 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4571</v>
+        <v>4602</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2019-05-13</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>333800000</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>72534</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1556,12 +1565,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1571,14 +1580,14 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>B号屋 (蓝塘道35号)</t>
+          <t>A号屋 (蓝塘道37号)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1597,7 +1606,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4602</v>
+        <v>4575</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1606,14 +1615,14 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2019-05-13</t>
+          <t>2019-03-19</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>333800000</v>
+        <v>338200000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>72534</v>
+        <v>73923</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1644,7 +1653,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>A号屋 (蓝塘道37号)</t>
+          <t>B号屋 (蓝塘道37号)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1663,7 +1672,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4575</v>
+        <v>4602</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1672,14 +1681,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2019-03-19</t>
+          <t>2018-02-26</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>338200000</v>
+        <v>303800000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>73923</v>
+        <v>66015</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1710,7 +1719,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>B号屋 (蓝塘道37号)</t>
+          <t>A号屋 (蓝塘道39号)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1729,7 +1738,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4602</v>
+        <v>4575</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1738,14 +1747,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2016-10-17</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>303800000</v>
+        <v>288300000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>66015</v>
+        <v>63016</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1776,7 +1785,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>A号屋 (蓝塘道39号)</t>
+          <t>B号屋 (蓝塘道39号)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1791,11 +1800,11 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4575</v>
+        <v>4602</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1804,14 +1813,14 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2016-10-17</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>288300000</v>
+        <v>339800000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>63016</v>
+        <v>73837</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1834,72 +1843,6 @@
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>B号屋 (蓝塘道39号)</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>4602</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>339800000</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>73837</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1977,7 +1920,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>18 套</t>
+          <t>17 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1992,7 +1935,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>15 套</t>
+          <t>14 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2197,15 +2140,7 @@
 $97,173/呎</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>B号屋 (蓝塘道33号)
-4602呎 (4+房)
-(24年-02月-08日)
-$2.30亿
-$49,978/呎</t>
-        </is>
-      </c>
+      <c r="G7" s="19" t="inlineStr"/>
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道35号)

--- a/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
+++ b/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
@@ -116,7 +116,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -159,12 +159,6 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -192,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -246,9 +240,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1451,7 +1442,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>A号屋 (蓝塘道35号)</t>
+          <t>B号屋 (蓝塘道33号)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1466,31 +1457,27 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4571</v>
+        <v>4602</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>230000000</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>49978</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1499,12 +1486,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1514,14 +1501,14 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>B号屋 (蓝塘道35号)</t>
+          <t>A号屋 (蓝塘道35号)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1536,27 +1523,31 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4602</v>
+        <v>4571</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2019-05-13</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>333800000</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>72534</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1565,12 +1556,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1580,14 +1571,14 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>A号屋 (蓝塘道37号)</t>
+          <t>B号屋 (蓝塘道35号)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1606,7 +1597,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4575</v>
+        <v>4602</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1615,14 +1606,14 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2019-03-19</t>
+          <t>2019-05-13</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>338200000</v>
+        <v>333800000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>73923</v>
+        <v>72534</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1653,7 +1644,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>B号屋 (蓝塘道37号)</t>
+          <t>A号屋 (蓝塘道37号)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1672,7 +1663,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4602</v>
+        <v>4575</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1681,14 +1672,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2019-03-19</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>303800000</v>
+        <v>338200000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>66015</v>
+        <v>73923</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1719,7 +1710,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>A号屋 (蓝塘道39号)</t>
+          <t>B号屋 (蓝塘道37号)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1738,7 +1729,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4575</v>
+        <v>4602</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1747,14 +1738,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2016-10-17</t>
+          <t>2018-02-26</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>288300000</v>
+        <v>303800000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>63016</v>
+        <v>66015</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1785,64 +1776,130 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>A号屋 (蓝塘道39号)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>4575</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>2016-10-17</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>288300000</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>63016</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>B号屋 (蓝塘道39号)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>3房</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E20" s="4" t="n">
         <v>4602</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H20" s="5" t="n">
         <v>339800000</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>73837</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1920,7 +1977,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>17 套</t>
+          <t>18 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1935,7 +1992,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>14 套</t>
+          <t>15 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2020,7 +2077,7 @@
         <is>
           <t>A号屋 (蓝塘道25号)
 4575呎 (4+房)
-(16年-12月-14日)
+(16年-12月)
 $3.02亿
 $65,967/呎</t>
         </is>
@@ -2029,7 +2086,7 @@
         <is>
           <t>A号屋 (蓝塘道27号)
 4575呎 (4+房)
-(18年-06月-11日)
+(18年-06月)
 $3.06亿
 $66,842/呎</t>
         </is>
@@ -2038,7 +2095,7 @@
         <is>
           <t>A号屋 (蓝塘道29号)
 4575呎 (4+房)
-(18年-04月-18日)
+(18年-04月)
 $3.28亿
 $71,694/呎</t>
         </is>
@@ -2047,7 +2104,7 @@
         <is>
           <t>A号屋 (蓝塘道31号)
 4575呎 (1房)
-(25年-12月-31日)
+(25年-12月)
 $4.47亿
 $97,747/呎</t>
         </is>
@@ -2056,7 +2113,7 @@
         <is>
           <t>A号屋 (蓝塘道33号)
 4575呎 (4+房)
-(25年-12月-21日)
+(25年-12月)
 $2.28亿
 $49,810/呎</t>
         </is>
@@ -2074,7 +2131,7 @@
         <is>
           <t>A号屋 (蓝塘道37号)
 4575呎 (4+房)
-(19年-03月-19日)
+(19年-03月)
 $3.38亿
 $73,923/呎</t>
         </is>
@@ -2083,7 +2140,7 @@
         <is>
           <t>A号屋 (蓝塘道39号)
 4575呎 (4+房)
-(16年-10月-17日)
+(16年-10月)
 $2.88亿
 $63,016/呎</t>
         </is>
@@ -2108,7 +2165,7 @@
         <is>
           <t>B号屋 (蓝塘道25号)
 4602呎 (4+房)
-(19年-05月-13日)
+(19年-05月)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -2117,7 +2174,7 @@
         <is>
           <t>B号屋 (蓝塘道27号)
 4602呎 (4+房)
-(18年-04月-11日)
+(18年-04月)
 $3.38亿
 $73,490/呎</t>
         </is>
@@ -2126,7 +2183,7 @@
         <is>
           <t>B号屋 (蓝塘道29号)
 4602呎 (4+房)
-(24年-06月-04日)
+(24年-06月)
 $2.50亿
 $54,324/呎</t>
         </is>
@@ -2135,17 +2192,25 @@
         <is>
           <t>B号屋 (蓝塘道31号)
 4602呎 (1房)
-(25年-12月-31日)
+(25年-12月)
 $4.47亿
 $97,173/呎</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>B号屋 (蓝塘道33号)
+4602呎 (4+房)
+(24年-02月)
+$2.30亿
+$49,978/呎</t>
+        </is>
+      </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道35号)
 4602呎 (4+房)
-(19年-05月-13日)
+(19年-05月)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -2154,7 +2219,7 @@
         <is>
           <t>B号屋 (蓝塘道37号)
 4602呎 (4+房)
-(18年-02月-26日)
+(18年-02月)
 $3.04亿
 $66,015/呎</t>
         </is>
@@ -2163,7 +2228,7 @@
         <is>
           <t>B号屋 (蓝塘道39号)
 4602呎 (3房)
-(21年-07月-25日)
+(21年-07月)
 $3.40亿
 $73,837/呎</t>
         </is>

--- a/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
+++ b/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
@@ -2077,7 +2077,7 @@
         <is>
           <t>A号屋 (蓝塘道25号)
 4575呎 (4+房)
-(16年-12月)
+(16年-12月-14日)
 $3.02亿
 $65,967/呎</t>
         </is>
@@ -2086,7 +2086,7 @@
         <is>
           <t>A号屋 (蓝塘道27号)
 4575呎 (4+房)
-(18年-06月)
+(18年-06月-11日)
 $3.06亿
 $66,842/呎</t>
         </is>
@@ -2095,7 +2095,7 @@
         <is>
           <t>A号屋 (蓝塘道29号)
 4575呎 (4+房)
-(18年-04月)
+(18年-04月-18日)
 $3.28亿
 $71,694/呎</t>
         </is>
@@ -2104,7 +2104,7 @@
         <is>
           <t>A号屋 (蓝塘道31号)
 4575呎 (1房)
-(25年-12月)
+(25年-12月-31日)
 $4.47亿
 $97,747/呎</t>
         </is>
@@ -2113,7 +2113,7 @@
         <is>
           <t>A号屋 (蓝塘道33号)
 4575呎 (4+房)
-(25年-12月)
+(25年-12月-21日)
 $2.28亿
 $49,810/呎</t>
         </is>
@@ -2131,7 +2131,7 @@
         <is>
           <t>A号屋 (蓝塘道37号)
 4575呎 (4+房)
-(19年-03月)
+(19年-03月-19日)
 $3.38亿
 $73,923/呎</t>
         </is>
@@ -2140,7 +2140,7 @@
         <is>
           <t>A号屋 (蓝塘道39号)
 4575呎 (4+房)
-(16年-10月)
+(16年-10月-17日)
 $2.88亿
 $63,016/呎</t>
         </is>
@@ -2165,7 +2165,7 @@
         <is>
           <t>B号屋 (蓝塘道25号)
 4602呎 (4+房)
-(19年-05月)
+(19年-05月-13日)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -2174,7 +2174,7 @@
         <is>
           <t>B号屋 (蓝塘道27号)
 4602呎 (4+房)
-(18年-04月)
+(18年-04月-11日)
 $3.38亿
 $73,490/呎</t>
         </is>
@@ -2183,7 +2183,7 @@
         <is>
           <t>B号屋 (蓝塘道29号)
 4602呎 (4+房)
-(24年-06月)
+(24年-06月-04日)
 $2.50亿
 $54,324/呎</t>
         </is>
@@ -2192,7 +2192,7 @@
         <is>
           <t>B号屋 (蓝塘道31号)
 4602呎 (1房)
-(25年-12月)
+(25年-12月-31日)
 $4.47亿
 $97,173/呎</t>
         </is>
@@ -2201,7 +2201,7 @@
         <is>
           <t>B号屋 (蓝塘道33号)
 4602呎 (4+房)
-(24年-02月)
+(24年-02月-08日)
 $2.30亿
 $49,978/呎</t>
         </is>
@@ -2210,7 +2210,7 @@
         <is>
           <t>B号屋 (蓝塘道35号)
 4602呎 (4+房)
-(19年-05月)
+(19年-05月-13日)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -2219,7 +2219,7 @@
         <is>
           <t>B号屋 (蓝塘道37号)
 4602呎 (4+房)
-(18年-02月)
+(18年-02月-26日)
 $3.04亿
 $66,015/呎</t>
         </is>
@@ -2228,7 +2228,7 @@
         <is>
           <t>B号屋 (蓝塘道39号)
 4602呎 (3房)
-(21年-07月)
+(21年-07月-25日)
 $3.40亿
 $73,837/呎</t>
         </is>
